--- a/information_request_forms/019_retail_workflow_query_contact_form--information_request_forms.xlsx
+++ b/information_request_forms/019_retail_workflow_query_contact_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales',_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales', 'value': 'sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'service',_'value':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Service', 'value': 'service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product',_'value':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product', 'value': 'product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'jim',_'value':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Jim', 'value': 'jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
